--- a/checklist_forms/028_ilr_application_checklist--checklist_forms.xlsx
+++ b/checklist_forms/028_ilr_application_checklist--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'active_student'}</t>
+          <t>active_student</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Active Student'}</t>
+          <t>Active Student</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'inactive_student'}</t>
+          <t>inactive_student</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Inactive Student'}</t>
+          <t>Inactive Student</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'allocated_student'}</t>
+          <t>allocated_student</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Allocated Student'}</t>
+          <t>Allocated Student</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'suspended_student'}</t>
+          <t>suspended_student</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Suspended Student'}</t>
+          <t>Suspended Student</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'graduating_student'}</t>
+          <t>graduating_student</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Graduating Student'}</t>
+          <t>Graduating Student</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'indefinite_leave_to_remain'}</t>
+          <t>indefinite_leave_to_remain</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Indefinite Leave to Remain'}</t>
+          <t>Indefinite Leave to Remain</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'leave_of_absence'}</t>
+          <t>leave_of_absence</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Leave of Absence'}</t>
+          <t>Leave of Absence</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'leave_of_absence_with_a_fixed_date'}</t>
+          <t>leave_of_absence_with_a_fixed_date</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Leave of Absence with a fixed date'}</t>
+          <t>Leave of Absence with a fixed date</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'no_further_action_required'}</t>
+          <t>no_further_action_required</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'No further action required'}</t>
+          <t>No further action required</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'review_by_admissions'}</t>
+          <t>review_by_admissions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Review by Admissions'}</t>
+          <t>Review by Admissions</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'review_by_student_support'}</t>
+          <t>review_by_student_support</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Review by Student Support'}</t>
+          <t>Review by Student Support</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'review_by_other'}</t>
+          <t>review_by_other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Review by other'}</t>
+          <t>Review by other</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'done'}</t>
+          <t>done</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Done'}</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'not_required'}</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Not Required'}</t>
+          <t>Not Required</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'due_soon'}</t>
+          <t>due_soon</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Due Soon'}</t>
+          <t>Due Soon</t>
         </is>
       </c>
     </row>
